--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836D93C9-205F-4882-ACA3-7A64B36E149B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3768028-AF4C-4FF9-92ED-1DFB03256265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -608,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA0C928-1468-4F9D-80ED-6D65B7AC10B3}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:K169"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" hidden="1" customWidth="1"/>
@@ -1273,6 +1271,11 @@
         <v>1</v>
       </c>
     </row>
+    <row r="169" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K169">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3768028-AF4C-4FF9-92ED-1DFB03256265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3188A9-AC91-41C8-B1CF-590723B26C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -606,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA0C928-1468-4F9D-80ED-6D65B7AC10B3}">
-  <dimension ref="A1:K169"/>
+  <dimension ref="A1:L169"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" hidden="1" customWidth="1"/>
@@ -1271,9 +1271,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="11:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="11:12" x14ac:dyDescent="0.3">
       <c r="K169">
         <v>1</v>
+      </c>
+      <c r="L169">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3188A9-AC91-41C8-B1CF-590723B26C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED43CAF8-EBBC-45F9-9712-505F26D72338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -606,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA0C928-1468-4F9D-80ED-6D65B7AC10B3}">
-  <dimension ref="A1:L169"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" hidden="1" customWidth="1"/>
@@ -1271,12 +1271,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="11:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K169">
         <v>1</v>
       </c>
       <c r="L169">
         <v>2</v>
+      </c>
+      <c r="M169">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED43CAF8-EBBC-45F9-9712-505F26D72338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D258ACE7-B619-43D1-927E-FC01345E9BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -606,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA0C928-1468-4F9D-80ED-6D65B7AC10B3}">
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" hidden="1" customWidth="1"/>
@@ -1271,7 +1271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="11:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="11:14" x14ac:dyDescent="0.3">
       <c r="K169">
         <v>1</v>
       </c>
@@ -1280,6 +1280,9 @@
       </c>
       <c r="M169">
         <v>3</v>
+      </c>
+      <c r="N169">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D258ACE7-B619-43D1-927E-FC01345E9BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D010E9F-35F1-4BA6-8127-EEBE45D83014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -606,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA0C928-1468-4F9D-80ED-6D65B7AC10B3}">
-  <dimension ref="A1:N169"/>
+  <dimension ref="A1:N170"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" hidden="1" customWidth="1"/>
@@ -1285,6 +1285,11 @@
         <v>4</v>
       </c>
     </row>
+    <row r="170" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K170">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D010E9F-35F1-4BA6-8127-EEBE45D83014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDF72D1-95DB-43D6-A59C-453751445519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -1289,6 +1289,9 @@
       <c r="K170">
         <v>5</v>
       </c>
+      <c r="L170">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDF72D1-95DB-43D6-A59C-453751445519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA44D40-E399-48D0-A178-5FC1B3217BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -1292,6 +1292,9 @@
       <c r="L170">
         <v>6</v>
       </c>
+      <c r="M170">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA44D40-E399-48D0-A178-5FC1B3217BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D170FB-5E9C-41B4-8B7E-AB393F07AB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -1295,6 +1295,9 @@
       <c r="M170">
         <v>7</v>
       </c>
+      <c r="N170">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D170FB-5E9C-41B4-8B7E-AB393F07AB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AC6A2B-5DF6-450C-AED5-86041559BFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -606,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA0C928-1468-4F9D-80ED-6D65B7AC10B3}">
-  <dimension ref="A1:N170"/>
+  <dimension ref="A1:N171"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" hidden="1" customWidth="1"/>
@@ -1299,6 +1299,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="171" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K171">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AC6A2B-5DF6-450C-AED5-86041559BFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E21887E-FE3F-49CA-A234-8896D0CFC59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -1303,6 +1303,9 @@
       <c r="K171">
         <v>9</v>
       </c>
+      <c r="L171">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E21887E-FE3F-49CA-A234-8896D0CFC59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D257BF-FC4E-4171-BD3A-156F22040517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -1306,6 +1306,9 @@
       <c r="L171">
         <v>10</v>
       </c>
+      <c r="M171">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D257BF-FC4E-4171-BD3A-156F22040517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB667B58-5926-4203-B7AE-A9E8B9B88A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -606,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA0C928-1468-4F9D-80ED-6D65B7AC10B3}">
-  <dimension ref="A1:N171"/>
+  <dimension ref="A1:N174"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" hidden="1" customWidth="1"/>
@@ -1310,6 +1310,11 @@
         <v>11</v>
       </c>
     </row>
+    <row r="174" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K174">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB667B58-5926-4203-B7AE-A9E8B9B88A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17748A94-EACA-4DC0-9DA7-C33972154B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -1314,6 +1314,9 @@
       <c r="K174">
         <v>1</v>
       </c>
+      <c r="L174">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17748A94-EACA-4DC0-9DA7-C33972154B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C0804C-09FA-4F67-B5B9-65B8A10B87E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -1317,6 +1317,9 @@
       <c r="L174">
         <v>2</v>
       </c>
+      <c r="M174">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C0804C-09FA-4F67-B5B9-65B8A10B87E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2384147-5FDB-4D71-BAD7-BBC2100876AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -1320,6 +1320,9 @@
       <c r="M174">
         <v>3</v>
       </c>
+      <c r="N174">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2384147-5FDB-4D71-BAD7-BBC2100876AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5397DE5A-5785-48BA-851D-F129EB785B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -606,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA0C928-1468-4F9D-80ED-6D65B7AC10B3}">
-  <dimension ref="A1:N174"/>
+  <dimension ref="A1:N175"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" hidden="1" customWidth="1"/>
@@ -1324,6 +1324,11 @@
         <v>4</v>
       </c>
     </row>
+    <row r="175" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K175">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5397DE5A-5785-48BA-851D-F129EB785B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD956B6-E64A-4343-B56E-2E145E92C01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -1328,6 +1328,9 @@
       <c r="K175">
         <v>5</v>
       </c>
+      <c r="L175">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD956B6-E64A-4343-B56E-2E145E92C01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0420A7A6-11A0-4CE6-A7EE-C26BA6A3D3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -1331,6 +1331,9 @@
       <c r="L175">
         <v>6</v>
       </c>
+      <c r="M175">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0420A7A6-11A0-4CE6-A7EE-C26BA6A3D3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A4170D-DAF8-4770-BE30-5658DEB3076C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -1334,6 +1334,9 @@
       <c r="M175">
         <v>7</v>
       </c>
+      <c r="N175">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A4170D-DAF8-4770-BE30-5658DEB3076C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1E35F9-AA9E-49B4-9F54-632DF4AFB643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -606,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA0C928-1468-4F9D-80ED-6D65B7AC10B3}">
-  <dimension ref="A1:N175"/>
+  <dimension ref="A1:N176"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" hidden="1" customWidth="1"/>
@@ -1338,6 +1338,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="176" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K176">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1E35F9-AA9E-49B4-9F54-632DF4AFB643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7649164-2814-4C92-B0E9-BA391D355200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -1342,6 +1342,9 @@
       <c r="K176">
         <v>9</v>
       </c>
+      <c r="L176">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
+++ b/Nivel Avanzado/Modulo9/BI primeros ejercicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\db\Nik Denilson\Cursos\EXCEL\Nivel Avanzado\Modulo9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7649164-2814-4C92-B0E9-BA391D355200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6014CFB5-D578-4D5D-9AA3-323627D8FD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97695EB7-5D60-4356-9820-794710C8B368}"/>
   </bookViews>
@@ -1345,6 +1345,9 @@
       <c r="L176">
         <v>10</v>
       </c>
+      <c r="M176">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
